--- a/main/ig/StructureDefinition-dmi-supplyrequest-entete-demande.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplyrequest-entete-demande.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-27T10:37:28+00:00</t>
+    <t>2026-03-05T09:47:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-supplyrequest-entete-demande.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplyrequest-entete-demande.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T09:47:44+00:00</t>
+    <t>2026-03-05T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-supplyrequest-entete-demande.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplyrequest-entete-demande.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1834" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1849" uniqueCount="373">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:00:25+00:00</t>
+    <t>2026-03-05T10:01:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -319,10 +319,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>SupplyRequest.implicitRules</t>
   </si>
   <si>
@@ -342,6 +349,9 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>SupplyRequest.language</t>
   </si>
   <si>
@@ -419,9 +429,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>SupplyRequest.extension</t>
   </si>
   <si>
@@ -442,6 +449,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -505,6 +522,9 @@
     <t>Status of the supply request.</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
@@ -540,6 +560,9 @@
     <t>Category of supply, e.g.  central, non-stock, etc. This is used to support work flows associated with the supply process.</t>
   </si>
   <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>example</t>
   </si>
   <si>
@@ -622,23 +645,10 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>SupplyRequest.item[x].extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -894,6 +904,16 @@
     <t>The amount that is being ordered of the indicated item.</t>
   </si>
   <si>
+    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
+  </si>
+  <si>
+    <t>SN (see also Range) or CQ</t>
+  </si>
+  <si>
     <t>.quantity</t>
   </si>
   <si>
@@ -1040,6 +1060,13 @@
   </si>
   <si>
     <t>The device, practitioner, etc. who initiated the request.</t>
+  </si>
+  <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Request.requester</t>
@@ -1934,10 +1961,10 @@
         <v>88</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -1946,7 +1973,7 @@
         <v>77</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="AN4" t="s" s="2">
         <v>77</v>
@@ -1954,10 +1981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1980,16 +2007,16 @@
         <v>89</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2039,7 +2066,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2048,10 +2075,10 @@
         <v>88</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -2060,7 +2087,7 @@
         <v>77</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>77</v>
@@ -2068,10 +2095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2094,16 +2121,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2129,13 +2156,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -2153,7 +2180,7 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -2162,10 +2189,10 @@
         <v>88</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -2174,7 +2201,7 @@
         <v>77</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>77</v>
@@ -2182,14 +2209,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2208,16 +2235,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2267,7 +2294,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2276,10 +2303,10 @@
         <v>88</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
@@ -2288,7 +2315,7 @@
         <v>77</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>77</v>
@@ -2296,14 +2323,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2322,16 +2349,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2381,7 +2408,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2402,7 +2429,7 @@
         <v>77</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>77</v>
@@ -2410,14 +2437,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2436,16 +2463,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2483,19 +2510,19 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2504,10 +2531,10 @@
         <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2516,7 +2543,7 @@
         <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>77</v>
@@ -2524,14 +2551,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2550,19 +2577,19 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2599,19 +2626,19 @@
         <v>77</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2620,10 +2647,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2632,7 +2659,7 @@
         <v>77</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>77</v>
@@ -2640,10 +2667,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2666,19 +2693,19 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2727,7 +2754,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2736,30 +2763,30 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2782,15 +2809,17 @@
         <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2815,13 +2844,13 @@
         <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>77</v>
@@ -2839,7 +2868,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2848,34 +2877,34 @@
         <v>88</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2894,15 +2923,17 @@
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -2927,32 +2958,32 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="Y13" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="Z13" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
       </c>
@@ -2960,30 +2991,30 @@
         <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3006,21 +3037,23 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q14" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="R14" t="s" s="2">
         <v>77</v>
@@ -3041,13 +3074,13 @@
         <v>77</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>77</v>
@@ -3065,7 +3098,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3074,30 +3107,30 @@
         <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3120,16 +3153,16 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3155,13 +3188,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3179,7 +3212,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>88</v>
@@ -3188,19 +3221,19 @@
         <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>77</v>
@@ -3208,10 +3241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3234,13 +3267,13 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3291,7 +3324,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3312,7 +3345,7 @@
         <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>196</v>
+        <v>109</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>77</v>
@@ -3320,14 +3353,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3346,16 +3379,16 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3393,19 +3426,19 @@
         <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>199</v>
+        <v>140</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>200</v>
+        <v>141</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>201</v>
+        <v>142</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3414,10 +3447,10 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
@@ -3426,7 +3459,7 @@
         <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>196</v>
+        <v>102</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
@@ -3434,10 +3467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3460,19 +3493,19 @@
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3509,17 +3542,17 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AC18" s="2"/>
       <c r="AD18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>201</v>
+        <v>142</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3528,19 +3561,19 @@
         <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
@@ -3548,13 +3581,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>77</v>
@@ -3576,19 +3609,19 @@
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3637,7 +3670,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3646,19 +3679,19 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
@@ -3666,10 +3699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3692,13 +3725,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3749,7 +3782,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3770,7 +3803,7 @@
         <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>196</v>
+        <v>109</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>77</v>
@@ -3778,14 +3811,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3804,16 +3837,16 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3851,19 +3884,19 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>199</v>
+        <v>140</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>200</v>
+        <v>141</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>201</v>
+        <v>142</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3872,10 +3905,10 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
@@ -3884,7 +3917,7 @@
         <v>77</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>196</v>
+        <v>102</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
@@ -3892,10 +3925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3918,19 +3951,19 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -3979,7 +4012,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3988,19 +4021,19 @@
         <v>88</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -4008,10 +4041,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4034,16 +4067,16 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4093,7 +4126,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4102,19 +4135,19 @@
         <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -4122,10 +4155,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4148,17 +4181,19 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O24" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4168,7 +4203,7 @@
         <v>77</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>77</v>
@@ -4207,7 +4242,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4216,19 +4251,19 @@
         <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4236,10 +4271,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4262,17 +4297,19 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O25" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4321,7 +4358,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4330,19 +4367,19 @@
         <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -4350,10 +4387,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4376,19 +4413,19 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4437,7 +4474,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4446,19 +4483,19 @@
         <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -4466,13 +4503,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>77</v>
@@ -4494,19 +4531,19 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4555,7 +4592,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4564,19 +4601,19 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
@@ -4584,10 +4621,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4610,13 +4647,13 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4667,7 +4704,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4688,7 +4725,7 @@
         <v>77</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>196</v>
+        <v>109</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -4696,14 +4733,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4722,16 +4759,16 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4769,19 +4806,19 @@
         <v>77</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>199</v>
+        <v>140</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>200</v>
+        <v>141</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>201</v>
+        <v>142</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4790,10 +4827,10 @@
         <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
@@ -4802,7 +4839,7 @@
         <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>196</v>
+        <v>102</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -4810,10 +4847,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4836,19 +4873,19 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4897,7 +4934,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4906,19 +4943,19 @@
         <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -4926,10 +4963,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4952,16 +4989,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5011,7 +5048,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5020,19 +5057,19 @@
         <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5040,10 +5077,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5066,17 +5103,19 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O32" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5086,7 +5125,7 @@
         <v>77</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>77</v>
@@ -5125,7 +5164,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5134,19 +5173,19 @@
         <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5154,10 +5193,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5180,17 +5219,19 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O33" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5239,7 +5280,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5248,19 +5289,19 @@
         <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5268,10 +5309,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5294,19 +5335,19 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5355,7 +5396,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5364,19 +5405,19 @@
         <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5384,10 +5425,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5410,19 +5451,19 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5471,7 +5512,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5480,19 +5521,19 @@
         <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5500,10 +5541,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5526,15 +5567,17 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5583,7 +5626,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>88</v>
@@ -5592,19 +5635,19 @@
         <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>100</v>
+        <v>289</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>77</v>
+        <v>290</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -5612,10 +5655,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5638,13 +5681,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5695,7 +5738,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5704,30 +5747,30 @@
         <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5750,13 +5793,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5807,7 +5850,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5828,7 +5871,7 @@
         <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>196</v>
+        <v>109</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -5836,14 +5879,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5862,16 +5905,16 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5909,19 +5952,19 @@
         <v>77</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5930,10 +5973,10 @@
         <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
@@ -5942,7 +5985,7 @@
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>196</v>
+        <v>102</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -5950,14 +5993,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5976,19 +6019,19 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6037,7 +6080,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6046,10 +6089,10 @@
         <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
@@ -6058,7 +6101,7 @@
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6066,10 +6109,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6092,15 +6135,17 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6125,10 +6170,10 @@
         <v>77</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="Z41" t="s" s="2">
         <v>77</v>
@@ -6149,7 +6194,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6158,30 +6203,30 @@
         <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6204,16 +6249,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6263,7 +6308,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6272,34 +6317,34 @@
         <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6318,13 +6363,13 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6375,7 +6420,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6384,34 +6429,34 @@
         <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6430,13 +6475,13 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6487,7 +6532,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6496,34 +6541,34 @@
         <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6542,15 +6587,17 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6599,7 +6646,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6608,34 +6655,34 @@
         <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>100</v>
+        <v>338</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6654,15 +6701,17 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L46" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6711,7 +6760,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6720,30 +6769,30 @@
         <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>338</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6766,15 +6815,17 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -6799,13 +6850,13 @@
         <v>77</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>77</v>
@@ -6823,7 +6874,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6832,30 +6883,30 @@
         <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6878,15 +6929,17 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="L48" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="M48" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -6935,7 +6988,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6944,30 +6997,30 @@
         <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>100</v>
+        <v>338</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6990,15 +7043,17 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7047,7 +7102,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7056,19 +7111,19 @@
         <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>100</v>
+        <v>338</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7076,10 +7131,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7102,15 +7157,17 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7159,7 +7216,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7168,19 +7225,19 @@
         <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>100</v>
+        <v>338</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>

--- a/main/ig/StructureDefinition-dmi-supplyrequest-entete-demande.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplyrequest-entete-demande.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1849" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1834" uniqueCount="365">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:01:25+00:00</t>
+    <t>2026-03-05T10:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -319,17 +319,10 @@
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>SupplyRequest.implicitRules</t>
   </si>
   <si>
@@ -349,9 +342,6 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>SupplyRequest.language</t>
   </si>
   <si>
@@ -429,6 +419,9 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>SupplyRequest.extension</t>
   </si>
   <si>
@@ -449,6 +442,195 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>SupplyRequest.modifierExtension</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>SupplyRequest.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Business Identifier for SupplyRequest</t>
+  </si>
+  <si>
+    <t>Business identifiers assigned to this SupplyRequest by the author and/or other systems. These identifiers remain constant as the resource is updated and propagates from server to server.</t>
+  </si>
+  <si>
+    <t>The identifier.type element is used to distinguish between the identifiers assigned by the requester/placer and the performer/filler.</t>
+  </si>
+  <si>
+    <t>Allows identification of the request as it is known by various participating systems and in a way that remains consistent across servers.</t>
+  </si>
+  <si>
+    <t>Request.identifier</t>
+  </si>
+  <si>
+    <t>ORC.2, ORC.3</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>SupplyRequest.status</t>
+  </si>
+  <si>
+    <t>draft | active | suspended +</t>
+  </si>
+  <si>
+    <t>Status of the supply request.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/supplyrequest-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Request.status</t>
+  </si>
+  <si>
+    <t>ORC.5</t>
+  </si>
+  <si>
+    <t>.status</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>SupplyRequest.category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kind
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>The kind of supply (central, non-stock, etc.)</t>
+  </si>
+  <si>
+    <t>Category of supply, e.g.  central, non-stock, etc. This is used to support work flows associated with the supply process.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Category of supply request.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/supplyrequest-kind|4.0.1</t>
+  </si>
+  <si>
+    <t>.code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>SupplyRequest.priority</t>
+  </si>
+  <si>
+    <t>routine | urgent | asap | stat</t>
+  </si>
+  <si>
+    <t>Indicates how quickly this SupplyRequest should be addressed with respect to other requests.</t>
+  </si>
+  <si>
+    <t>If missing, this task should be performed with normal priority</t>
+  </si>
+  <si>
+    <t>Identifies the level of importance to be assigned to actioning the request.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
+  </si>
+  <si>
+    <t>Request.priority</t>
+  </si>
+  <si>
+    <t>TQ1.9</t>
+  </si>
+  <si>
+    <t>.priorityCode</t>
+  </si>
+  <si>
+    <t>FiveWs.grade</t>
+  </si>
+  <si>
+    <t>SupplyRequest.item[x]</t>
+  </si>
+  <si>
+    <t>Medication, Substance, or Device requested to be supplied</t>
+  </si>
+  <si>
+    <t>The item that is requested to be supplied. This is either a link to a resource representing the details of the item or a code that identifies the item from a known list.</t>
+  </si>
+  <si>
+    <t>Note that there's a difference between a prescription - an instruction to take a medication, along with a (sometimes) implicit supply, and an explicit request to supply, with no explicit instructions.</t>
+  </si>
+  <si>
+    <t>The item that was requested.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/supply-item|4.0.1</t>
+  </si>
+  <si>
+    <t>Request.code</t>
+  </si>
+  <si>
+    <t>SupplyRequest.item[x].id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>SupplyRequest.item[x].extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
     <t xml:space="preserve">value:url}
 </t>
   </si>
@@ -459,198 +641,6 @@
     <t>open</t>
   </si>
   <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>SupplyRequest.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>SupplyRequest.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Business Identifier for SupplyRequest</t>
-  </si>
-  <si>
-    <t>Business identifiers assigned to this SupplyRequest by the author and/or other systems. These identifiers remain constant as the resource is updated and propagates from server to server.</t>
-  </si>
-  <si>
-    <t>The identifier.type element is used to distinguish between the identifiers assigned by the requester/placer and the performer/filler.</t>
-  </si>
-  <si>
-    <t>Allows identification of the request as it is known by various participating systems and in a way that remains consistent across servers.</t>
-  </si>
-  <si>
-    <t>Request.identifier</t>
-  </si>
-  <si>
-    <t>ORC.2, ORC.3</t>
-  </si>
-  <si>
-    <t>.identifier</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>SupplyRequest.status</t>
-  </si>
-  <si>
-    <t>draft | active | suspended +</t>
-  </si>
-  <si>
-    <t>Status of the supply request.</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/supplyrequest-status|4.0.1</t>
-  </si>
-  <si>
-    <t>Request.status</t>
-  </si>
-  <si>
-    <t>ORC.5</t>
-  </si>
-  <si>
-    <t>.status</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>SupplyRequest.category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kind
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>The kind of supply (central, non-stock, etc.)</t>
-  </si>
-  <si>
-    <t>Category of supply, e.g.  central, non-stock, etc. This is used to support work flows associated with the supply process.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>Category of supply request.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/supplyrequest-kind|4.0.1</t>
-  </si>
-  <si>
-    <t>.code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>SupplyRequest.priority</t>
-  </si>
-  <si>
-    <t>routine | urgent | asap | stat</t>
-  </si>
-  <si>
-    <t>Indicates how quickly this SupplyRequest should be addressed with respect to other requests.</t>
-  </si>
-  <si>
-    <t>If missing, this task should be performed with normal priority</t>
-  </si>
-  <si>
-    <t>Identifies the level of importance to be assigned to actioning the request.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
-  </si>
-  <si>
-    <t>Request.priority</t>
-  </si>
-  <si>
-    <t>TQ1.9</t>
-  </si>
-  <si>
-    <t>.priorityCode</t>
-  </si>
-  <si>
-    <t>FiveWs.grade</t>
-  </si>
-  <si>
-    <t>SupplyRequest.item[x]</t>
-  </si>
-  <si>
-    <t>Medication, Substance, or Device requested to be supplied</t>
-  </si>
-  <si>
-    <t>The item that is requested to be supplied. This is either a link to a resource representing the details of the item or a code that identifies the item from a known list.</t>
-  </si>
-  <si>
-    <t>Note that there's a difference between a prescription - an instruction to take a medication, along with a (sometimes) implicit supply, and an explicit request to supply, with no explicit instructions.</t>
-  </si>
-  <si>
-    <t>The item that was requested.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/supply-item|4.0.1</t>
-  </si>
-  <si>
-    <t>Request.code</t>
-  </si>
-  <si>
-    <t>SupplyRequest.item[x].id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>SupplyRequest.item[x].extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -904,16 +894,6 @@
     <t>The amount that is being ordered of the indicated item.</t>
   </si>
   <si>
-    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
-  </si>
-  <si>
     <t>.quantity</t>
   </si>
   <si>
@@ -1060,13 +1040,6 @@
   </si>
   <si>
     <t>The device, practitioner, etc. who initiated the request.</t>
-  </si>
-  <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Request.requester</t>
@@ -1961,11 +1934,11 @@
         <v>88</v>
       </c>
       <c r="AI4" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ4" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
       </c>
@@ -1973,7 +1946,7 @@
         <v>77</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AN4" t="s" s="2">
         <v>77</v>
@@ -1981,10 +1954,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2007,16 +1980,16 @@
         <v>89</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L5" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="L5" t="s" s="2">
+      <c r="N5" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2066,7 +2039,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2075,11 +2048,11 @@
         <v>88</v>
       </c>
       <c r="AI5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ5" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
       </c>
@@ -2087,7 +2060,7 @@
         <v>77</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>77</v>
@@ -2095,10 +2068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2121,16 +2094,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="M6" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="N6" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="L6" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2156,32 +2129,32 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="Y6" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="Y6" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="Z6" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>118</v>
-      </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
@@ -2189,11 +2162,11 @@
         <v>88</v>
       </c>
       <c r="AI6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ6" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
@@ -2201,7 +2174,7 @@
         <v>77</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>77</v>
@@ -2209,14 +2182,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2235,16 +2208,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="N7" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="L7" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N7" t="s" s="2">
-        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2294,7 +2267,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2303,11 +2276,11 @@
         <v>88</v>
       </c>
       <c r="AI7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ7" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
@@ -2315,7 +2288,7 @@
         <v>77</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>77</v>
@@ -2323,14 +2296,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2349,16 +2322,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="N8" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="L8" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2408,7 +2381,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2429,7 +2402,7 @@
         <v>77</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>77</v>
@@ -2437,14 +2410,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2463,16 +2436,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2510,19 +2483,19 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2531,10 +2504,10 @@
         <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2543,7 +2516,7 @@
         <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>77</v>
@@ -2551,14 +2524,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2577,19 +2550,19 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2626,19 +2599,19 @@
         <v>77</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2647,10 +2620,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2659,7 +2632,7 @@
         <v>77</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>77</v>
@@ -2667,10 +2640,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2693,19 +2666,19 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2754,7 +2727,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2763,30 +2736,30 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ11" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK11" t="s" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2809,17 +2782,15 @@
         <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2844,67 +2815,67 @@
         <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="Y12" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF12" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG12" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH12" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ12" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK12" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AL12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AM12" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="Z12" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AG12" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH12" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI12" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ12" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK12" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>168</v>
-      </c>
       <c r="AN12" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2923,17 +2894,15 @@
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -2958,13 +2927,13 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>77</v>
@@ -2982,7 +2951,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2991,30 +2960,30 @@
         <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ13" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3037,23 +3006,21 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q14" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="R14" t="s" s="2">
         <v>77</v>
@@ -3074,13 +3041,13 @@
         <v>77</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>77</v>
@@ -3098,39 +3065,39 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK14" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AL14" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AG14" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK14" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>188</v>
-      </c>
       <c r="AM14" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3153,16 +3120,16 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3188,13 +3155,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3212,7 +3179,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>88</v>
@@ -3221,19 +3188,19 @@
         <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ15" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK15" t="s" s="2">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>77</v>
@@ -3241,10 +3208,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3267,13 +3234,13 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3324,7 +3291,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3345,7 +3312,7 @@
         <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>109</v>
+        <v>196</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>77</v>
@@ -3353,14 +3320,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3379,16 +3346,16 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M17" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N17" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3426,19 +3393,19 @@
         <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>140</v>
+        <v>199</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>141</v>
+        <v>200</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>142</v>
+        <v>201</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3447,10 +3414,10 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
@@ -3459,7 +3426,7 @@
         <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>102</v>
+        <v>196</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
@@ -3467,10 +3434,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3493,19 +3460,19 @@
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3542,17 +3509,17 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="AC18" s="2"/>
       <c r="AD18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>142</v>
+        <v>201</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3561,19 +3528,19 @@
         <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ18" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
@@ -3581,13 +3548,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>77</v>
@@ -3609,19 +3576,19 @@
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3670,7 +3637,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3679,19 +3646,19 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ19" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
@@ -3699,10 +3666,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3725,13 +3692,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3782,7 +3749,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3803,7 +3770,7 @@
         <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>109</v>
+        <v>196</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>77</v>
@@ -3811,14 +3778,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3837,16 +3804,16 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3884,19 +3851,19 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>140</v>
+        <v>199</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>141</v>
+        <v>200</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>142</v>
+        <v>201</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3905,10 +3872,10 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
@@ -3917,7 +3884,7 @@
         <v>77</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>102</v>
+        <v>196</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
@@ -3925,10 +3892,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3951,19 +3918,19 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="O22" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4012,7 +3979,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4021,19 +3988,19 @@
         <v>88</v>
       </c>
       <c r="AI22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ22" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -4041,10 +4008,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4067,16 +4034,16 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4126,7 +4093,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4135,19 +4102,19 @@
         <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ23" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -4155,10 +4122,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4181,19 +4148,17 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4203,67 +4168,67 @@
         <v>77</v>
       </c>
       <c r="S24" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="T24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF24" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4271,10 +4236,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4297,19 +4262,17 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4358,7 +4321,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4367,19 +4330,19 @@
         <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ25" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -4387,10 +4350,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4413,19 +4376,19 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4474,7 +4437,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4483,19 +4446,19 @@
         <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ26" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -4503,13 +4466,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>77</v>
@@ -4531,19 +4494,19 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4592,7 +4555,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4601,19 +4564,19 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ27" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
@@ -4621,10 +4584,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4647,13 +4610,13 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4704,7 +4667,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4725,7 +4688,7 @@
         <v>77</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>109</v>
+        <v>196</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -4733,14 +4696,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4759,16 +4722,16 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N29" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4806,19 +4769,19 @@
         <v>77</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>140</v>
+        <v>199</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>141</v>
+        <v>200</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>142</v>
+        <v>201</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4827,10 +4790,10 @@
         <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
@@ -4839,7 +4802,7 @@
         <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>102</v>
+        <v>196</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -4847,10 +4810,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4873,19 +4836,19 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="O30" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4934,7 +4897,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4943,19 +4906,19 @@
         <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ30" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -4963,10 +4926,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4989,16 +4952,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5048,7 +5011,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5057,19 +5020,19 @@
         <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ31" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5077,10 +5040,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5103,19 +5066,17 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5125,7 +5086,7 @@
         <v>77</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>77</v>
@@ -5164,7 +5125,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5173,19 +5134,19 @@
         <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ32" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5193,10 +5154,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5219,19 +5180,17 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5280,7 +5239,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5289,19 +5248,19 @@
         <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ33" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5309,10 +5268,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5335,19 +5294,19 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5396,7 +5355,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5405,19 +5364,19 @@
         <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ34" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5425,10 +5384,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5451,19 +5410,19 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="O35" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5512,7 +5471,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5521,19 +5480,19 @@
         <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ35" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5541,10 +5500,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5567,17 +5526,15 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5626,7 +5583,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>88</v>
@@ -5635,19 +5592,19 @@
         <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ36" t="s" s="2">
-        <v>289</v>
-      </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>290</v>
+        <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -5655,10 +5612,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5681,13 +5638,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5738,7 +5695,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5747,30 +5704,30 @@
         <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ37" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5793,13 +5750,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5850,7 +5807,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5871,7 +5828,7 @@
         <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>109</v>
+        <v>196</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -5879,14 +5836,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5905,16 +5862,16 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5952,19 +5909,19 @@
         <v>77</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>140</v>
+        <v>77</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>141</v>
+        <v>77</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5973,10 +5930,10 @@
         <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
@@ -5985,7 +5942,7 @@
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>102</v>
+        <v>196</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -5993,14 +5950,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6019,19 +5976,19 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6080,7 +6037,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6089,10 +6046,10 @@
         <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
@@ -6101,7 +6058,7 @@
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6109,10 +6066,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6135,17 +6092,15 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6170,10 +6125,10 @@
         <v>77</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="Z41" t="s" s="2">
         <v>77</v>
@@ -6194,7 +6149,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6203,30 +6158,30 @@
         <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ41" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6249,16 +6204,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6308,7 +6263,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6317,34 +6272,34 @@
         <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ42" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6363,13 +6318,13 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6420,43 +6375,43 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AG43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>320</v>
-      </c>
       <c r="AM43" t="s" s="2">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6475,13 +6430,13 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6532,43 +6487,43 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="AG44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>329</v>
-      </c>
       <c r="AM44" t="s" s="2">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6587,17 +6542,15 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6646,43 +6599,43 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AG45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>340</v>
-      </c>
       <c r="AM45" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6701,17 +6654,15 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>339</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6760,7 +6711,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6769,30 +6720,30 @@
         <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ46" t="s" s="2">
-        <v>338</v>
-      </c>
       <c r="AK46" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6815,17 +6766,15 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -6850,13 +6799,13 @@
         <v>77</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>77</v>
@@ -6874,7 +6823,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6883,30 +6832,30 @@
         <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ47" t="s" s="2">
-        <v>101</v>
-      </c>
       <c r="AK47" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6929,17 +6878,15 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -6988,7 +6935,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6997,30 +6944,30 @@
         <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ48" t="s" s="2">
-        <v>338</v>
-      </c>
       <c r="AK48" t="s" s="2">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7043,17 +6990,15 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7102,7 +7047,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7111,19 +7056,19 @@
         <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ49" t="s" s="2">
-        <v>338</v>
-      </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7131,10 +7076,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7157,17 +7102,15 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7216,7 +7159,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7225,19 +7168,19 @@
         <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="AJ50" t="s" s="2">
-        <v>338</v>
-      </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>

--- a/main/ig/StructureDefinition-dmi-supplyrequest-entete-demande.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplyrequest-entete-demande.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:22:34+00:00</t>
+    <t>2026-03-05T10:23:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-dmi-supplyrequest-entete-demande.xlsx
+++ b/main/ig/StructureDefinition-dmi-supplyrequest-entete-demande.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1834" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1849" uniqueCount="373">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T10:23:55+00:00</t>
+    <t>2026-03-05T10:25:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -266,7 +266,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -319,10 +319,17 @@
     <t>Resource.meta</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>SupplyRequest.implicitRules</t>
   </si>
   <si>
@@ -342,6 +349,9 @@
     <t>Resource.implicitRules</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>SupplyRequest.language</t>
   </si>
   <si>
@@ -419,9 +429,6 @@
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>SupplyRequest.extension</t>
   </si>
   <si>
@@ -442,6 +449,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
@@ -505,6 +522,9 @@
     <t>Status of the supply request.</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>required</t>
   </si>
   <si>
@@ -540,6 +560,9 @@
     <t>Category of supply, e.g.  central, non-stock, etc. This is used to support work flows associated with the supply process.</t>
   </si>
   <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>example</t>
   </si>
   <si>
@@ -622,23 +645,10 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>SupplyRequest.item[x].extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -894,6 +904,16 @@
     <t>The amount that is being ordered of the indicated item.</t>
   </si>
   <si>
+    <t>The context of use may frequently define what kind of quantity this is and therefore what kind of units can be used. The context of use may also restrict the values for the comparator.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
+  </si>
+  <si>
+    <t>SN (see also Range) or CQ</t>
+  </si>
+  <si>
     <t>.quantity</t>
   </si>
   <si>
@@ -1040,6 +1060,13 @@
   </si>
   <si>
     <t>The device, practitioner, etc. who initiated the request.</t>
+  </si>
+  <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
   </si>
   <si>
     <t>Request.requester</t>
@@ -1934,10 +1961,10 @@
         <v>88</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -1946,7 +1973,7 @@
         <v>77</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="AN4" t="s" s="2">
         <v>77</v>
@@ -1954,10 +1981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1980,16 +2007,16 @@
         <v>89</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2039,7 +2066,7 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2048,10 +2075,10 @@
         <v>88</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -2060,7 +2087,7 @@
         <v>77</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AN5" t="s" s="2">
         <v>77</v>
@@ -2068,10 +2095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2094,16 +2121,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2129,13 +2156,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -2153,7 +2180,7 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
@@ -2162,10 +2189,10 @@
         <v>88</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -2174,7 +2201,7 @@
         <v>77</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AN6" t="s" s="2">
         <v>77</v>
@@ -2182,14 +2209,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2208,16 +2235,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2267,7 +2294,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2276,10 +2303,10 @@
         <v>88</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
@@ -2288,7 +2315,7 @@
         <v>77</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>77</v>
@@ -2296,14 +2323,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2322,16 +2349,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2381,7 +2408,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2402,7 +2429,7 @@
         <v>77</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>77</v>
@@ -2410,14 +2437,14 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -2436,16 +2463,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2483,19 +2510,19 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2504,10 +2531,10 @@
         <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2516,7 +2543,7 @@
         <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="AN9" t="s" s="2">
         <v>77</v>
@@ -2524,14 +2551,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2550,19 +2577,19 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>77</v>
@@ -2599,19 +2626,19 @@
         <v>77</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2620,10 +2647,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2632,7 +2659,7 @@
         <v>77</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>77</v>
@@ -2640,10 +2667,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2666,19 +2693,19 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2727,7 +2754,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2736,30 +2763,30 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2782,15 +2809,17 @@
         <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2815,13 +2844,13 @@
         <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>77</v>
@@ -2839,7 +2868,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2848,34 +2877,34 @@
         <v>88</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2894,15 +2923,17 @@
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -2927,32 +2958,32 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="Y13" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="Z13" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>164</v>
-      </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
       </c>
@@ -2960,30 +2991,30 @@
         <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3006,21 +3037,23 @@
         <v>89</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>183</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q14" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="R14" t="s" s="2">
         <v>77</v>
@@ -3041,13 +3074,13 @@
         <v>77</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>77</v>
@@ -3065,7 +3098,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3074,30 +3107,30 @@
         <v>88</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3120,16 +3153,16 @@
         <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3155,13 +3188,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3179,7 +3212,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>88</v>
@@ -3188,19 +3221,19 @@
         <v>88</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>77</v>
@@ -3208,10 +3241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3234,13 +3267,13 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3291,7 +3324,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3312,7 +3345,7 @@
         <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>196</v>
+        <v>109</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>77</v>
@@ -3320,14 +3353,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3346,16 +3379,16 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3393,19 +3426,19 @@
         <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>199</v>
+        <v>140</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>200</v>
+        <v>141</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>201</v>
+        <v>142</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3414,10 +3447,10 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
@@ -3426,7 +3459,7 @@
         <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>196</v>
+        <v>102</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
@@ -3434,10 +3467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3460,19 +3493,19 @@
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3509,17 +3542,17 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="AC18" s="2"/>
       <c r="AD18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>201</v>
+        <v>142</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3528,19 +3561,19 @@
         <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
@@ -3548,13 +3581,13 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>77</v>
@@ -3576,19 +3609,19 @@
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3637,7 +3670,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3646,19 +3679,19 @@
         <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
@@ -3666,10 +3699,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3692,13 +3725,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3749,7 +3782,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3770,7 +3803,7 @@
         <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>196</v>
+        <v>109</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>77</v>
@@ -3778,14 +3811,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -3804,16 +3837,16 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3851,19 +3884,19 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>199</v>
+        <v>140</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>200</v>
+        <v>141</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>201</v>
+        <v>142</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3872,10 +3905,10 @@
         <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
@@ -3884,7 +3917,7 @@
         <v>77</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>196</v>
+        <v>102</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
@@ -3892,10 +3925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3918,19 +3951,19 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -3979,7 +4012,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3988,19 +4021,19 @@
         <v>88</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -4008,10 +4041,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4034,16 +4067,16 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4093,7 +4126,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4102,19 +4135,19 @@
         <v>88</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -4122,10 +4155,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4148,17 +4181,19 @@
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O24" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4168,7 +4203,7 @@
         <v>77</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>77</v>
@@ -4207,7 +4242,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4216,19 +4251,19 @@
         <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4236,10 +4271,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4262,17 +4297,19 @@
         <v>89</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O25" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4321,7 +4358,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4330,19 +4367,19 @@
         <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -4350,10 +4387,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4376,19 +4413,19 @@
         <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4437,7 +4474,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4446,19 +4483,19 @@
         <v>88</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -4466,13 +4503,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>77</v>
@@ -4494,19 +4531,19 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4555,7 +4592,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4564,19 +4601,19 @@
         <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>77</v>
@@ -4584,10 +4621,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4610,13 +4647,13 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4667,7 +4704,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4688,7 +4725,7 @@
         <v>77</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>196</v>
+        <v>109</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -4696,14 +4733,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4722,16 +4759,16 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4769,19 +4806,19 @@
         <v>77</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>199</v>
+        <v>140</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>200</v>
+        <v>141</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>201</v>
+        <v>142</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4790,10 +4827,10 @@
         <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
@@ -4802,7 +4839,7 @@
         <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>196</v>
+        <v>102</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -4810,10 +4847,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4836,19 +4873,19 @@
         <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4897,7 +4934,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4906,19 +4943,19 @@
         <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -4926,10 +4963,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4952,16 +4989,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5011,7 +5048,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5020,19 +5057,19 @@
         <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5040,10 +5077,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5066,17 +5103,19 @@
         <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O32" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5086,7 +5125,7 @@
         <v>77</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>77</v>
@@ -5125,7 +5164,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5134,19 +5173,19 @@
         <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5154,10 +5193,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5180,17 +5219,19 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O33" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5239,7 +5280,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5248,19 +5289,19 @@
         <v>88</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -5268,10 +5309,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5294,19 +5335,19 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5355,7 +5396,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5364,19 +5405,19 @@
         <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5384,10 +5425,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5410,19 +5451,19 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5471,7 +5512,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5480,19 +5521,19 @@
         <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5500,10 +5541,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5526,15 +5567,17 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5583,7 +5626,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>88</v>
@@ -5592,19 +5635,19 @@
         <v>88</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>100</v>
+        <v>289</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>77</v>
+        <v>290</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -5612,10 +5655,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5638,13 +5681,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5695,7 +5738,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5704,30 +5747,30 @@
         <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5750,13 +5793,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5807,7 +5850,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5828,7 +5871,7 @@
         <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>196</v>
+        <v>109</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -5836,14 +5879,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5862,16 +5905,16 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5909,19 +5952,19 @@
         <v>77</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>77</v>
+        <v>140</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5930,10 +5973,10 @@
         <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
@@ -5942,7 +5985,7 @@
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>196</v>
+        <v>102</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -5950,14 +5993,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5976,19 +6019,19 @@
         <v>89</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6037,7 +6080,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6046,10 +6089,10 @@
         <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
@@ -6058,7 +6101,7 @@
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6066,10 +6109,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6092,15 +6135,17 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6125,10 +6170,10 @@
         <v>77</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="Z41" t="s" s="2">
         <v>77</v>
@@ -6149,7 +6194,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6158,30 +6203,30 @@
         <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6204,16 +6249,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6263,7 +6308,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6272,34 +6317,34 @@
         <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6318,13 +6363,13 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6375,7 +6420,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6384,34 +6429,34 @@
         <v>88</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6430,13 +6475,13 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6487,7 +6532,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6496,34 +6541,34 @@
         <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6542,15 +6587,17 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6599,7 +6646,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6608,34 +6655,34 @@
         <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>100</v>
+        <v>338</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6654,15 +6701,17 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L46" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6711,7 +6760,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6720,30 +6769,30 @@
         <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>338</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6766,15 +6815,17 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -6799,13 +6850,13 @@
         <v>77</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>77</v>
@@ -6823,7 +6874,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6832,30 +6883,30 @@
         <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6878,15 +6929,17 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="L48" t="s" s="2">
-        <v>345</v>
-      </c>
       <c r="M48" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -6935,7 +6988,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6944,30 +6997,30 @@
         <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>100</v>
+        <v>338</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6990,15 +7043,17 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7047,7 +7102,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7056,19 +7111,19 @@
         <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>100</v>
+        <v>338</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7076,10 +7131,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7102,15 +7157,17 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7159,7 +7216,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7168,19 +7225,19 @@
         <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>100</v>
+        <v>338</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
